--- a/data/reports/2024-05-27/2024-05-27_duplicates.xlsx
+++ b/data/reports/2024-05-27/2024-05-27_duplicates.xlsx
@@ -145,7 +145,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -161,28 +161,28 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -225,10 +225,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,6 +318,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -340,13 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -469,10 +469,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -483,16 +493,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007488</t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -606,15 +606,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -622,24 +640,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -670,7 +670,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -681,32 +681,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -726,6 +700,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -754,7 +754,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -764,6 +764,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -780,12 +786,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005569</t>
@@ -836,7 +836,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
+    <t>RMD0005297</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -849,6 +849,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
+  </si>
+  <si>
     <t>Syed Omar Farooq Shah</t>
   </si>
   <si>
@@ -858,13 +864,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -878,6 +878,22 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>187 Plymouth Ave
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -891,23 +907,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>187 Plymouth Ave
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -993,7 +993,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1003,16 +1003,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1022,6 +1022,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1035,12 +1041,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1074,7 +1074,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1084,12 +1084,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1097,6 +1091,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008611</t>
   </si>
   <si>
@@ -1116,25 +1116,25 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008610</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -6126,16 +6126,28 @@
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -6143,16 +6155,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -6176,28 +6188,16 @@
         <v>46</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6474,9 +6474,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
@@ -6487,14 +6489,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6521,7 +6525,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6530,13 +6534,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
@@ -6547,9 +6549,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6568,55 +6568,41 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6628,32 +6614,46 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6679,54 +6679,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6743,33 +6729,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -6935,13 +6935,13 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>127</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7420,55 +7420,61 @@
         <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1">
         <v>30758643</v>
@@ -7480,34 +7486,28 @@
         <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>194</v>
@@ -7517,10 +7517,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -7549,7 +7549,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7595,7 +7595,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -7613,14 +7613,14 @@
         <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -7662,45 +7662,33 @@
       <c r="I33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1">
         <v>31064850</v>
@@ -7718,30 +7706,42 @@
         <v>209</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>30</v>
@@ -7873,48 +7873,34 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B38" s="1">
         <v>31124688</v>
@@ -7933,25 +7919,39 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -8102,45 +8102,33 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31294614</v>
@@ -8160,24 +8148,36 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8209,48 +8209,42 @@
       <c r="H43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1">
         <v>31356652</v>
@@ -8271,14 +8265,18 @@
         <v>268</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>277</v>
       </c>
@@ -8286,22 +8284,24 @@
         <v>27</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V44" s="1" t="s">
         <v>278</v>
       </c>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>30</v>
@@ -8627,9 +8627,15 @@
       <c r="F51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -8673,15 +8679,9 @@
       <c r="F52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -8720,55 +8720,41 @@
         <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1">
         <v>31445216</v>
@@ -8780,32 +8766,46 @@
         <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8940,7 +8940,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -8957,12 +8957,12 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="1">
         <v>31457815</v>
@@ -8986,7 +8986,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9071,38 +9071,50 @@
         <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R60" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1">
         <v>31475270</v>
@@ -9117,41 +9129,29 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9198,7 +9198,7 @@
         <v>354</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>30</v>
@@ -9304,7 +9304,7 @@
         <v>366</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>30</v>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>30</v>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>30</v>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>30</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="P78" s="1"/>
       <c r="Q78" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>30</v>
@@ -10073,7 +10073,7 @@
         <v>428</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>433</v>
@@ -10133,7 +10133,7 @@
         <v>245</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>440</v>
@@ -10189,7 +10189,7 @@
         <v>448</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>446</v>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>30</v>
@@ -10291,7 +10291,7 @@
         <v>30</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>458</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O83" s="1" t="s">
         <v>462</v>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>30</v>
@@ -10573,7 +10573,7 @@
         <v>30</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>30</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="P91" s="1"/>
       <c r="Q91" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R91" s="1" t="s">
         <v>30</v>
@@ -10821,7 +10821,7 @@
         <v>30</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -10861,7 +10861,7 @@
         <v>30</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>28</v>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R96" s="1" t="s">
         <v>26</v>
@@ -11045,7 +11045,7 @@
         <v>59</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M97" s="1" t="s">
         <v>526</v>
@@ -11428,10 +11428,10 @@
         <v>567</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>566</v>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="P104" s="1"/>
       <c r="Q104" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R104" s="1" t="s">
         <v>30</v>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="P108" s="1"/>
       <c r="Q108" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R108" s="1" t="s">
         <v>30</v>
@@ -11814,13 +11814,13 @@
         <v>27</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J111" s="1" t="s">
         <v>611</v>
@@ -11935,7 +11935,7 @@
         <v>626</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>622</v>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="P116" s="1"/>
       <c r="Q116" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R116" s="1" t="s">
         <v>30</v>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="P122" s="1"/>
       <c r="Q122" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R122" s="1" t="s">
         <v>30</v>
@@ -12752,7 +12752,7 @@
       </c>
       <c r="P128" s="1"/>
       <c r="Q128" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R128" s="1" t="s">
         <v>30</v>
@@ -12797,7 +12797,7 @@
         <v>717</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M129" s="1"/>
       <c r="N129" s="1" t="s">
@@ -12850,7 +12850,7 @@
         <v>723</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L130" s="1" t="s">
         <v>724</v>
@@ -12940,7 +12940,7 @@
         <v>27</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P133" s="1"/>
       <c r="Q133" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R133" s="1" t="s">
         <v>30</v>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="P134" s="1"/>
       <c r="Q134" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R134" s="1" t="s">
         <v>26</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>749</v>
@@ -13124,7 +13124,7 @@
       </c>
       <c r="P135" s="1"/>
       <c r="Q135" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R135" s="1" t="s">
         <v>30</v>
@@ -13155,7 +13155,7 @@
         <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
@@ -13167,11 +13167,11 @@
         <v>59</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M136" s="1"/>
       <c r="N136" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O136" s="1" t="s">
         <v>757</v>
@@ -13359,7 +13359,7 @@
         <v>30</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
@@ -13368,21 +13368,21 @@
         <v>775</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>203</v>
       </c>
       <c r="M140" s="1"/>
       <c r="N140" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O140" s="1" t="s">
         <v>776</v>
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R140" s="1" t="s">
         <v>30</v>
@@ -13467,7 +13467,7 @@
         <v>59</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M142" s="1"/>
       <c r="N142" s="1" t="s">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R142" s="1" t="s">
         <v>30</v>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R143" s="1" t="s">
         <v>26</v>
@@ -13563,7 +13563,7 @@
         <v>30</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
@@ -13605,7 +13605,7 @@
         <v>30</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>28</v>
@@ -13629,14 +13629,14 @@
         <v>800</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O145" s="1" t="s">
         <v>801</v>
       </c>
       <c r="P145" s="1"/>
       <c r="Q145" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R145" s="1" t="s">
         <v>30</v>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="P147" s="1"/>
       <c r="Q147" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R147" s="1" t="s">
         <v>30</v>
@@ -13797,7 +13797,7 @@
         <v>821</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M148" s="1" t="s">
         <v>822</v>
@@ -13929,7 +13929,7 @@
         <v>30</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -13947,14 +13947,14 @@
         <v>837</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O151" s="1" t="s">
         <v>838</v>
       </c>
       <c r="P151" s="1"/>
       <c r="Q151" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R151" s="1" t="s">
         <v>30</v>
@@ -14043,7 +14043,7 @@
         <v>30</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -14052,21 +14052,21 @@
         <v>846</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L153" s="1" t="s">
         <v>847</v>
       </c>
       <c r="M153" s="1"/>
       <c r="N153" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O153" s="1" t="s">
         <v>848</v>
       </c>
       <c r="P153" s="1"/>
       <c r="Q153" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R153" s="1" t="s">
         <v>30</v>
@@ -14225,7 +14225,7 @@
         <v>293</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M156" s="1" t="s">
         <v>865</v>
@@ -14267,7 +14267,7 @@
         <v>30</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -14285,14 +14285,14 @@
         <v>871</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O157" s="1" t="s">
         <v>872</v>
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>30</v>
@@ -14324,13 +14324,13 @@
         <v>27</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>875</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J158" s="1"/>
       <c r="K158" s="1"/>
@@ -14367,7 +14367,7 @@
         <v>30</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>878</v>
@@ -14571,7 +14571,7 @@
         <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
@@ -14583,18 +14583,18 @@
         <v>900</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M163" s="1"/>
       <c r="N163" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O163" s="1" t="s">
         <v>901</v>
       </c>
       <c r="P163" s="1"/>
       <c r="Q163" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R163" s="1" t="s">
         <v>30</v>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="P164" s="1"/>
       <c r="Q164" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>30</v>
@@ -14701,7 +14701,7 @@
         <v>59</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M165" s="1" t="s">
         <v>916</v>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="P165" s="1"/>
       <c r="Q165" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R165" s="1" t="s">
         <v>30</v>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="P166" s="1"/>
       <c r="Q166" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>30</v>
@@ -14817,7 +14817,7 @@
         <v>930</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M167" s="1"/>
       <c r="N167" s="1" t="s">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>30</v>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="P172" s="1"/>
       <c r="Q172" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>30</v>
@@ -15267,7 +15267,7 @@
         <v>165</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M175" s="1" t="s">
         <v>979</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>30</v>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="P176" s="1"/>
       <c r="Q176" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>26</v>
@@ -15376,13 +15376,13 @@
         <v>27</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J177" s="1" t="s">
         <v>993</v>
@@ -15391,7 +15391,7 @@
         <v>59</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>992</v>
@@ -15404,7 +15404,7 @@
       </c>
       <c r="P177" s="1"/>
       <c r="Q177" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R177" s="1" t="s">
         <v>30</v>
@@ -15510,7 +15510,7 @@
         <v>1007</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L179" s="1" t="s">
         <v>1008</v>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="P180" s="1"/>
       <c r="Q180" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>30</v>
@@ -15845,7 +15845,7 @@
         <v>1038</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M185" s="1" t="s">
         <v>1039</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="P185" s="1"/>
       <c r="Q185" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R185" s="1" t="s">
         <v>30</v>
@@ -15969,7 +15969,7 @@
         <v>1056</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M187" s="1" t="s">
         <v>1053</v>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P189" s="1"/>
       <c r="Q189" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>30</v>
@@ -16134,13 +16134,13 @@
         <v>27</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H190" s="1" t="s">
         <v>1073</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>1074</v>
@@ -16149,7 +16149,7 @@
         <v>1075</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M190" s="1" t="s">
         <v>1072</v>
@@ -16215,7 +16215,7 @@
         <v>245</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>1081</v>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="P191" s="1"/>
       <c r="Q191" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>30</v>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>26</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="P193" s="1"/>
       <c r="Q193" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R193" s="1" t="s">
         <v>26</v>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R194" s="1" t="s">
         <v>30</v>
@@ -16564,13 +16564,13 @@
         <v>27</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H197" s="1" t="s">
         <v>1122</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J197" s="1"/>
       <c r="K197" s="1"/>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="P201" s="1"/>
       <c r="Q201" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R201" s="1" t="s">
         <v>30</v>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="P203" s="1"/>
       <c r="Q203" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R203" s="1" t="s">
         <v>30</v>
@@ -17048,7 +17048,7 @@
         <v>1177</v>
       </c>
       <c r="Q205" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>26</v>
@@ -17086,7 +17086,7 @@
         <v>1181</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>1182</v>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="P206" s="1"/>
       <c r="Q206" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R206" s="1" t="s">
         <v>30</v>
@@ -17166,7 +17166,7 @@
         <v>1191</v>
       </c>
       <c r="Q207" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>26</v>
@@ -17230,7 +17230,7 @@
         <v>1200</v>
       </c>
       <c r="Q208" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R208" s="1" t="s">
         <v>26</v>
@@ -17288,7 +17288,7 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R209" s="1" t="s">
         <v>30</v>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="P210" s="1"/>
       <c r="Q210" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>30</v>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>30</v>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R212" s="1" t="s">
         <v>30</v>
@@ -17505,16 +17505,16 @@
         <v>30</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>1237</v>
@@ -17529,7 +17529,7 @@
         <v>1236</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>1239</v>
@@ -17571,7 +17571,7 @@
         <v>30</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>1242</v>
@@ -17591,7 +17591,7 @@
         <v>1236</v>
       </c>
       <c r="N214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O214" s="1" t="s">
         <v>1239</v>
@@ -17646,10 +17646,10 @@
         <v>1249</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M215" s="1" t="s">
         <v>1250</v>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R217" s="1" t="s">
         <v>30</v>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>30</v>
@@ -17928,7 +17928,7 @@
         <v>1005</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H220" s="1"/>
       <c r="I220" s="1"/>
@@ -17952,7 +17952,7 @@
       </c>
       <c r="P220" s="1"/>
       <c r="Q220" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R220" s="1" t="s">
         <v>30</v>
@@ -17997,7 +17997,7 @@
         <v>1282</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>1283</v>
@@ -18010,7 +18010,7 @@
       </c>
       <c r="P221" s="1"/>
       <c r="Q221" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R221" s="1" t="s">
         <v>30</v>
@@ -18061,7 +18061,7 @@
         <v>1289</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M222" s="1" t="s">
         <v>1290</v>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="P223" s="1"/>
       <c r="Q223" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R223" s="1" t="s">
         <v>30</v>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>30</v>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>30</v>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R226" s="1" t="s">
         <v>30</v>
@@ -18433,7 +18433,7 @@
         <v>165</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M228" s="1" t="s">
         <v>1334</v>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>30</v>
@@ -18484,13 +18484,13 @@
         <v>27</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>1340</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>1341</v>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>30</v>
@@ -18572,7 +18572,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>30</v>
@@ -18625,7 +18625,7 @@
         <v>428</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M231" s="1" t="s">
         <v>1357</v>
@@ -18638,7 +18638,7 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R231" s="1" t="s">
         <v>30</v>
@@ -18770,7 +18770,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>30</v>
@@ -18818,7 +18818,7 @@
         <v>1381</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L234" s="1" t="s">
         <v>1382</v>
@@ -18834,7 +18834,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>30</v>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P235" s="1"/>
       <c r="Q235" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R235" s="1" t="s">
         <v>30</v>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="P236" s="1"/>
       <c r="Q236" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R236" s="1" t="s">
         <v>30</v>
@@ -19078,7 +19078,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>30</v>
@@ -19193,7 +19193,7 @@
         <v>1418</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M240" s="1" t="s">
         <v>1423</v>
@@ -19266,7 +19266,7 @@
       </c>
       <c r="P241" s="1"/>
       <c r="Q241" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R241" s="1" t="s">
         <v>26</v>
@@ -19310,10 +19310,10 @@
         <v>1434</v>
       </c>
       <c r="K242" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M242" s="1" t="s">
         <v>1433</v>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="P242" s="1"/>
       <c r="Q242" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R242" s="1" t="s">
         <v>30</v>
@@ -19422,13 +19422,13 @@
         <v>27</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>1440</v>
@@ -19576,7 +19576,7 @@
         <v>1463</v>
       </c>
       <c r="Q246" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R246" s="1" t="s">
         <v>30</v>
@@ -19625,7 +19625,7 @@
         <v>293</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M247" s="1" t="s">
         <v>1467</v>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="P247" s="1"/>
       <c r="Q247" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R247" s="1" t="s">
         <v>30</v>
@@ -19687,7 +19687,7 @@
         <v>293</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1467</v>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>30</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="P250" s="1"/>
       <c r="Q250" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>30</v>
@@ -20231,7 +20231,7 @@
         <v>1534</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M257" s="1" t="s">
         <v>1530</v>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="P257" s="1"/>
       <c r="Q257" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R257" s="1" t="s">
         <v>30</v>
@@ -20293,7 +20293,7 @@
         <v>1534</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M258" s="1" t="s">
         <v>1540</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="P258" s="1"/>
       <c r="Q258" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R258" s="1" t="s">
         <v>30</v>
@@ -20417,7 +20417,7 @@
         <v>639</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>1555</v>
@@ -20430,7 +20430,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>30</v>
@@ -20466,13 +20466,13 @@
         <v>27</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J261" s="1" t="s">
         <v>1561</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R261" s="1" t="s">
         <v>30</v>
@@ -20541,7 +20541,7 @@
         <v>293</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M262" s="1" t="s">
         <v>1569</v>
@@ -20605,7 +20605,7 @@
         <v>1578</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M263" s="1" t="s">
         <v>1579</v>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>30</v>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>30</v>
@@ -20729,7 +20729,7 @@
         <v>428</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M265" s="1" t="s">
         <v>1591</v>
@@ -20791,7 +20791,7 @@
         <v>428</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1591</v>
@@ -20853,7 +20853,7 @@
         <v>59</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1603</v>
@@ -20917,7 +20917,7 @@
         <v>59</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1610</v>
@@ -20968,13 +20968,13 @@
         <v>209</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H269" s="1" t="s">
         <v>1619</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>1620</v>
@@ -20998,7 +20998,7 @@
         <v>1624</v>
       </c>
       <c r="Q269" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R269" s="1" t="s">
         <v>30</v>
@@ -21036,13 +21036,13 @@
         <v>209</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>1619</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>1620</v>
@@ -21066,7 +21066,7 @@
         <v>1624</v>
       </c>
       <c r="Q270" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>30</v>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="P271" s="1"/>
       <c r="Q271" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>30</v>
@@ -21190,7 +21190,7 @@
       </c>
       <c r="P272" s="1"/>
       <c r="Q272" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>30</v>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>30</v>
@@ -21312,7 +21312,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>30</v>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="P276" s="1"/>
       <c r="Q276" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>30</v>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>30</v>
@@ -21736,7 +21736,7 @@
         <v>1704</v>
       </c>
       <c r="Q281" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R281" s="1" t="s">
         <v>30</v>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="P282" s="1"/>
       <c r="Q282" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R282" s="1" t="s">
         <v>30</v>
@@ -21833,7 +21833,7 @@
         <v>30</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>1719</v>
@@ -21847,20 +21847,20 @@
         <v>1721</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M283" s="1" t="s">
         <v>1718</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O283" s="1" t="s">
         <v>1722</v>
       </c>
       <c r="P283" s="1"/>
       <c r="Q283" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R283" s="1" t="s">
         <v>30</v>
@@ -21893,7 +21893,7 @@
         <v>30</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G284" s="1"/>
       <c r="H284" s="1"/>
@@ -21905,20 +21905,20 @@
         <v>1726</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M284" s="1" t="s">
         <v>1718</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O284" s="1" t="s">
         <v>1727</v>
       </c>
       <c r="P284" s="1"/>
       <c r="Q284" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R284" s="1" t="s">
         <v>30</v>
